--- a/HPWinner_Intake_Questionnaire_v2.xlsx
+++ b/HPWinner_Intake_Questionnaire_v2.xlsx
@@ -126,7 +126,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -148,11 +148,55 @@
         <color rgb="00BFBFBF"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -188,6 +232,8 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -816,7 +862,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F75"/>
+  <dimension ref="A1:F87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -865,6 +911,11 @@
           <t>0. 提交信息（必填）</t>
         </is>
       </c>
+      <c r="B2" s="17" t="n"/>
+      <c r="C2" s="17" t="n"/>
+      <c r="D2" s="17" t="n"/>
+      <c r="E2" s="17" t="n"/>
+      <c r="F2" s="18" t="n"/>
     </row>
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
@@ -1084,6 +1135,11 @@
           <t>A. 项目范围</t>
         </is>
       </c>
+      <c r="B11" s="17" t="n"/>
+      <c r="C11" s="17" t="n"/>
+      <c r="D11" s="17" t="n"/>
+      <c r="E11" s="17" t="n"/>
+      <c r="F11" s="18" t="n"/>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="6" t="inlineStr">
@@ -1315,6 +1371,11 @@
           <t>B. 现状成本基线（按年度）</t>
         </is>
       </c>
+      <c r="B21" s="17" t="n"/>
+      <c r="C21" s="17" t="n"/>
+      <c r="D21" s="17" t="n"/>
+      <c r="E21" s="17" t="n"/>
+      <c r="F21" s="18" t="n"/>
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="6" t="inlineStr">
@@ -1438,6 +1499,11 @@
           <t>C. 用电与运行状况（关键LaaS输入）</t>
         </is>
       </c>
+      <c r="B27" s="17" t="n"/>
+      <c r="C27" s="17" t="n"/>
+      <c r="D27" s="17" t="n"/>
+      <c r="E27" s="17" t="n"/>
+      <c r="F27" s="18" t="n"/>
     </row>
     <row r="28" ht="30" customHeight="1">
       <c r="A28" s="6" t="inlineStr">
@@ -1661,6 +1727,11 @@
           <t>D. 维护与运维</t>
         </is>
       </c>
+      <c r="B37" s="17" t="n"/>
+      <c r="C37" s="17" t="n"/>
+      <c r="D37" s="17" t="n"/>
+      <c r="E37" s="17" t="n"/>
+      <c r="F37" s="18" t="n"/>
     </row>
     <row r="38" ht="30" customHeight="1">
       <c r="A38" s="6" t="inlineStr">
@@ -1776,6 +1847,11 @@
           <t>E. 土建与硬件（新建/改造项目填写）</t>
         </is>
       </c>
+      <c r="B43" s="17" t="n"/>
+      <c r="C43" s="17" t="n"/>
+      <c r="D43" s="17" t="n"/>
+      <c r="E43" s="17" t="n"/>
+      <c r="F43" s="18" t="n"/>
     </row>
     <row r="44" ht="30" customHeight="1">
       <c r="A44" s="6" t="inlineStr">
@@ -1887,6 +1963,11 @@
           <t>F. 网络连接与数据（AI路灯专项）</t>
         </is>
       </c>
+      <c r="B49" s="17" t="n"/>
+      <c r="C49" s="17" t="n"/>
+      <c r="D49" s="17" t="n"/>
+      <c r="E49" s="17" t="n"/>
+      <c r="F49" s="18" t="n"/>
     </row>
     <row r="50" ht="30" customHeight="1">
       <c r="A50" s="6" t="inlineStr">
@@ -1990,6 +2071,11 @@
           <t>G. 客户财务状况</t>
         </is>
       </c>
+      <c r="B54" s="17" t="n"/>
+      <c r="C54" s="17" t="n"/>
+      <c r="D54" s="17" t="n"/>
+      <c r="E54" s="17" t="n"/>
+      <c r="F54" s="18" t="n"/>
     </row>
     <row r="55" ht="30" customHeight="1">
       <c r="A55" s="6" t="inlineStr">
@@ -2109,6 +2195,11 @@
           <t>H. 合同偏好</t>
         </is>
       </c>
+      <c r="B60" s="17" t="n"/>
+      <c r="C60" s="17" t="n"/>
+      <c r="D60" s="17" t="n"/>
+      <c r="E60" s="17" t="n"/>
+      <c r="F60" s="18" t="n"/>
     </row>
     <row r="61" ht="30" customHeight="1">
       <c r="A61" s="6" t="inlineStr">
@@ -2212,6 +2303,11 @@
           <t>J. 现有合同与约束（仅在已有EMC/ESCO时填写）</t>
         </is>
       </c>
+      <c r="B65" s="17" t="n"/>
+      <c r="C65" s="17" t="n"/>
+      <c r="D65" s="17" t="n"/>
+      <c r="E65" s="17" t="n"/>
+      <c r="F65" s="18" t="n"/>
     </row>
     <row r="66" ht="30" customHeight="1">
       <c r="A66" s="6" t="inlineStr">
@@ -2327,6 +2423,11 @@
           <t>K. 竞争与置信度</t>
         </is>
       </c>
+      <c r="B71" s="17" t="n"/>
+      <c r="C71" s="17" t="n"/>
+      <c r="D71" s="17" t="n"/>
+      <c r="E71" s="17" t="n"/>
+      <c r="F71" s="18" t="n"/>
     </row>
     <row r="72" ht="30" customHeight="1">
       <c r="A72" s="6" t="inlineStr">
@@ -2423,6 +2524,210 @@
       <c r="D75" s="11" t="inlineStr"/>
       <c r="E75" s="12" t="n"/>
       <c r="F75" s="10" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>B6</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>项目总投资额（一次性CAPEX，含硬件+安装+管沟+备用金）— 能源托管专用</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>本币</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>A5b</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>灯杆总数（柱数）</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>柱</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>A7a</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>钠灯（HPS）灯具数量</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>盏</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>A7b</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>LED 灯具数量</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>盏</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>A7c</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>其它灯具数量（中杆灯/景观灯等）</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>盏</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>B1a</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>上一年度电费支出</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>本币/年</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>B1b</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>前年度电费支出</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>本币/年</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>B2a</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>上一年度运维支出</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>本币/年</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>B2b</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>前年度运维支出</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>本币/年</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>C7</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>客户调研得出的节能率（如：一次X% 二次Y%）</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>G6</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>客户期望年度节省额（年节省目标）</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>本币/年</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>H5</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>预期合同总金额（合同期合计）</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>本币</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -2528,7 +2833,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F75"/>
+  <dimension ref="A1:F87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -2577,6 +2882,11 @@
           <t>0. Submission metadata (required)</t>
         </is>
       </c>
+      <c r="B2" s="17" t="n"/>
+      <c r="C2" s="17" t="n"/>
+      <c r="D2" s="17" t="n"/>
+      <c r="E2" s="17" t="n"/>
+      <c r="F2" s="18" t="n"/>
     </row>
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
@@ -2796,6 +3106,11 @@
           <t>A. Project scope</t>
         </is>
       </c>
+      <c r="B11" s="17" t="n"/>
+      <c r="C11" s="17" t="n"/>
+      <c r="D11" s="17" t="n"/>
+      <c r="E11" s="17" t="n"/>
+      <c r="F11" s="18" t="n"/>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="6" t="inlineStr">
@@ -3027,6 +3342,11 @@
           <t>B. Current cost baseline (annualized)</t>
         </is>
       </c>
+      <c r="B21" s="17" t="n"/>
+      <c r="C21" s="17" t="n"/>
+      <c r="D21" s="17" t="n"/>
+      <c r="E21" s="17" t="n"/>
+      <c r="F21" s="18" t="n"/>
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="6" t="inlineStr">
@@ -3150,6 +3470,11 @@
           <t>C. Electricity &amp; operating profile (critical LaaS inputs)</t>
         </is>
       </c>
+      <c r="B27" s="17" t="n"/>
+      <c r="C27" s="17" t="n"/>
+      <c r="D27" s="17" t="n"/>
+      <c r="E27" s="17" t="n"/>
+      <c r="F27" s="18" t="n"/>
     </row>
     <row r="28" ht="30" customHeight="1">
       <c r="A28" s="6" t="inlineStr">
@@ -3373,6 +3698,11 @@
           <t>D. Maintenance &amp; O&amp;M</t>
         </is>
       </c>
+      <c r="B37" s="17" t="n"/>
+      <c r="C37" s="17" t="n"/>
+      <c r="D37" s="17" t="n"/>
+      <c r="E37" s="17" t="n"/>
+      <c r="F37" s="18" t="n"/>
     </row>
     <row r="38" ht="30" customHeight="1">
       <c r="A38" s="6" t="inlineStr">
@@ -3488,6 +3818,11 @@
           <t>E. Civil works &amp; hardware (for New / Retrofit projects)</t>
         </is>
       </c>
+      <c r="B43" s="17" t="n"/>
+      <c r="C43" s="17" t="n"/>
+      <c r="D43" s="17" t="n"/>
+      <c r="E43" s="17" t="n"/>
+      <c r="F43" s="18" t="n"/>
     </row>
     <row r="44" ht="30" customHeight="1">
       <c r="A44" s="6" t="inlineStr">
@@ -3599,6 +3934,11 @@
           <t>F. Connectivity &amp; data (AI streetlight specifics)</t>
         </is>
       </c>
+      <c r="B49" s="17" t="n"/>
+      <c r="C49" s="17" t="n"/>
+      <c r="D49" s="17" t="n"/>
+      <c r="E49" s="17" t="n"/>
+      <c r="F49" s="18" t="n"/>
     </row>
     <row r="50" ht="30" customHeight="1">
       <c r="A50" s="6" t="inlineStr">
@@ -3702,6 +4042,11 @@
           <t>G. Customer financial posture</t>
         </is>
       </c>
+      <c r="B54" s="17" t="n"/>
+      <c r="C54" s="17" t="n"/>
+      <c r="D54" s="17" t="n"/>
+      <c r="E54" s="17" t="n"/>
+      <c r="F54" s="18" t="n"/>
     </row>
     <row r="55" ht="30" customHeight="1">
       <c r="A55" s="6" t="inlineStr">
@@ -3821,6 +4166,11 @@
           <t>H. Contract preferences</t>
         </is>
       </c>
+      <c r="B60" s="17" t="n"/>
+      <c r="C60" s="17" t="n"/>
+      <c r="D60" s="17" t="n"/>
+      <c r="E60" s="17" t="n"/>
+      <c r="F60" s="18" t="n"/>
     </row>
     <row r="61" ht="30" customHeight="1">
       <c r="A61" s="6" t="inlineStr">
@@ -3924,6 +4274,11 @@
           <t>J. Existing contracts &amp; constraints (only if existing EMC/ESCO)</t>
         </is>
       </c>
+      <c r="B65" s="17" t="n"/>
+      <c r="C65" s="17" t="n"/>
+      <c r="D65" s="17" t="n"/>
+      <c r="E65" s="17" t="n"/>
+      <c r="F65" s="18" t="n"/>
     </row>
     <row r="66" ht="30" customHeight="1">
       <c r="A66" s="6" t="inlineStr">
@@ -4039,6 +4394,11 @@
           <t>K. Competition &amp; data confidence</t>
         </is>
       </c>
+      <c r="B71" s="17" t="n"/>
+      <c r="C71" s="17" t="n"/>
+      <c r="D71" s="17" t="n"/>
+      <c r="E71" s="17" t="n"/>
+      <c r="F71" s="18" t="n"/>
     </row>
     <row r="72" ht="30" customHeight="1">
       <c r="A72" s="6" t="inlineStr">
@@ -4135,6 +4495,210 @@
       <c r="D75" s="11" t="inlineStr"/>
       <c r="E75" s="12" t="n"/>
       <c r="F75" s="10" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>B6</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Total project investment (one-time CAPEX, all-in incl. hardware + installation + trenching + contingency) — for 能源托管 only</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Local currency</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>A5b</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Total pole count</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Poles (count)</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>A7a</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>HPS fixture count</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Fixtures (count)</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>A7b</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>LED fixture count</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Fixtures (count)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>A7c</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Other fixture count (high-pole / decorative)</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Fixtures (count)</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>B1a</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Last year (Y-1) electricity bill</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>LC/yr</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>B1b</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Year before (Y-2) electricity bill</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>LC/yr</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>B2a</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Last year (Y-1) O&amp;M cost</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>LC/yr</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>B2b</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Year before (Y-2) O&amp;M cost</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>LC/yr</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>C7</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Customer-surveyed savings rates (e.g. primary X% secondary Y%)</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>G6</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Customer expected annual savings target</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>LC/yr</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>H5</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Expected total contract value (over full term)</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Local currency</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -5666,7 +6230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E64"/>
+  <dimension ref="A1:E76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7404,6 +7968,330 @@
         </is>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>B6</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>project_investment_cny</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Yes (能源托管)</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>cost_baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>A5b</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>pole_count</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>scope</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>A7a</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>existing_fixtures_hps</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>scope</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>A7b</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>existing_fixtures_led</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>scope</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>A7c</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>existing_fixtures_other</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>scope</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>B1a</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>annual_electricity_y_minus_1</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Yes (trend)</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>cost_baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>B1b</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>annual_electricity_y_minus_2</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Yes (trend)</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>cost_baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>B2a</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>annual_om_y_minus_1</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Yes (trend)</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>cost_baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>B2b</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>annual_om_y_minus_2</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Yes (trend)</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>cost_baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>C7</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>surveyed_savings_rates_text</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>operating_profile</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>G6</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>expected_annual_savings</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Yes (能源托管)</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>financials</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>H5</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>contract_total_value</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Yes (能源托管)</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>contract</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/HPWinner_Intake_Questionnaire_v2.xlsx
+++ b/HPWinner_Intake_Questionnaire_v2.xlsx
@@ -862,7 +862,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F87"/>
+  <dimension ref="A1:F89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -2613,12 +2613,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>B1a</t>
+          <t>B1c</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>上一年度电费支出</t>
+          <t>B1c 历史趋势：最早年度电费（全区/审计口径，如2023；与下方「本项目」B1 无关）</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2630,12 +2630,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>B1b</t>
+          <t>B1a</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>前年度电费支出</t>
+          <t>上一年度电费支出</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2647,12 +2647,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>B2a</t>
+          <t>B1b</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>上一年度运维支出</t>
+          <t>前年度电费支出</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2664,12 +2664,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>B2b</t>
+          <t>B2c</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>前年度运维支出</t>
+          <t>B2c 历史趋势：与上列电费同顺位的最早年度运维支出（含人工与维修等，与 B1c 同年）</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2681,29 +2681,29 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>B2a</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>客户调研得出的节能率（如：一次X% 二次Y%）</t>
+          <t>上一年度运维支出</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>本币/年</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>G6</t>
+          <t>B2b</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>客户期望年度节省额（年节省目标）</t>
+          <t>前年度运维支出</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -2715,15 +2715,49 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
+          <t>C7</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>客户调研得出的节能率（如：一次X% 二次Y%）</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>G6</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>客户期望年度节省额（年节省目标）</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>本币/年</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
           <t>H5</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
+      <c r="B89" t="inlineStr">
         <is>
           <t>预期合同总金额（合同期合计）</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
+      <c r="C89" t="inlineStr">
         <is>
           <t>本币</t>
         </is>
@@ -2833,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F87"/>
+  <dimension ref="A1:F89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -4584,12 +4618,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>B1a</t>
+          <t>B1c</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Last year (Y-1) electricity bill</t>
+          <t>B1c Historic trend: oldest-year electricity (city/audit scope, e.g. 2023; not the project baseline B1 below)</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -4601,12 +4635,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>B1b</t>
+          <t>B1a</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Year before (Y-2) electricity bill</t>
+          <t>Last year (Y-1) electricity bill</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -4618,12 +4652,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>B2a</t>
+          <t>B1b</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Last year (Y-1) O&amp;M cost</t>
+          <t>Year before (Y-2) electricity bill</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -4635,12 +4669,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>B2b</t>
+          <t>B2c</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Year before (Y-2) O&amp;M cost</t>
+          <t>B2c Historic trend: O&amp;M for the same oldest year as B1c (aligned row)</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -4652,29 +4686,29 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>B2a</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Customer-surveyed savings rates (e.g. primary X% secondary Y%)</t>
+          <t>Last year (Y-1) O&amp;M cost</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Text</t>
+          <t>LC/yr</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>G6</t>
+          <t>B2b</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Customer expected annual savings target</t>
+          <t>Year before (Y-2) O&amp;M cost</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -4686,15 +4720,49 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
+          <t>C7</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Customer-surveyed savings rates (e.g. primary X% secondary Y%)</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>G6</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Customer expected annual savings target</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>LC/yr</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
           <t>H5</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
+      <c r="B89" t="inlineStr">
         <is>
           <t>Expected total contract value (over full term)</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
+      <c r="C89" t="inlineStr">
         <is>
           <t>Local currency</t>
         </is>
@@ -6230,7 +6298,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E76"/>
+  <dimension ref="A1:E78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -8133,12 +8201,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>B1b</t>
+          <t>B1c</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>annual_electricity_y_minus_2</t>
+          <t>annual_electricity_y_minus_3</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -8160,12 +8228,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>B2a</t>
+          <t>B1b</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>annual_om_y_minus_1</t>
+          <t>annual_electricity_y_minus_2</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -8187,12 +8255,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>B2b</t>
+          <t>B2a</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>annual_om_y_minus_2</t>
+          <t>annual_om_y_minus_1</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -8214,39 +8282,39 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>B2c</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>surveyed_savings_rates_text</t>
+          <t>annual_om_y_minus_3</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>number</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes (trend)</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>operating_profile</t>
+          <t>cost_baseline</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>G6</t>
+          <t>B2b</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>expected_annual_savings</t>
+          <t>annual_om_y_minus_2</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -8256,37 +8324,91 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Yes (能源托管)</t>
+          <t>Yes (trend)</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>financials</t>
+          <t>cost_baseline</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
+          <t>C7</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>surveyed_savings_rates_text</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>operating_profile</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>G6</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>expected_annual_savings</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Yes (能源托管)</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>financials</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
           <t>H5</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="B78" t="inlineStr">
         <is>
           <t>contract_total_value</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
+      <c r="C78" t="inlineStr">
         <is>
           <t>number</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr">
+      <c r="D78" t="inlineStr">
         <is>
           <t>Yes (能源托管)</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
+      <c r="E78" t="inlineStr">
         <is>
           <t>contract</t>
         </is>
